--- a/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,7</t>
+          <t>0,0; 49,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,15</t>
+          <t>0,0; 42,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 37,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,51</t>
+          <t>0,0; 42,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,13</t>
+          <t>0,0; 65,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,38</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 33,01</t>
+          <t>4,25; 32,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 38,95</t>
+          <t>4,25; 37,8</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,4</t>
+          <t>0,0; 28,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,69</t>
+          <t>0,0; 60,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,5</t>
+          <t>0,0; 46,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 60,44</t>
+          <t>7,9; 60,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,51</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,05</t>
+          <t>0,0; 19,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 50,2</t>
+          <t>10,12; 50,31</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,5</t>
+          <t>0,0; 58,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,01</t>
+          <t>0,0; 39,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,12</t>
+          <t>0,0; 52,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,29</t>
+          <t>0,0; 51,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,83</t>
+          <t>0,0; 51,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,7</t>
+          <t>0,0; 70,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 42,2</t>
+          <t>5,6; 41,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 30,25</t>
+          <t>4,0; 30,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 50,07</t>
+          <t>5,42; 46,77</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,81</t>
+          <t>0,0; 28,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 33,36</t>
+          <t>3,67; 32,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 28,01</t>
+          <t>5,37; 28,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 30,32</t>
+          <t>3,91; 30,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 51,78</t>
+          <t>17,26; 53,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 23,72</t>
+          <t>4,13; 22,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 38,4</t>
+          <t>13,48; 36,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,69</t>
+          <t>2,88; 16,78</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 46,1</t>
+          <t>5,69; 45,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 47,99</t>
+          <t>5,71; 47,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,89</t>
+          <t>0,0; 28,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,88</t>
+          <t>0,0; 35,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 29,22</t>
+          <t>4,01; 33,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 33,52</t>
+          <t>3,72; 33,91</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 75,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1237,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,33</t>
+          <t>0,0; 68,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,74; 83,74</t>
+          <t>14,41; 83,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,1</t>
+          <t>0,0; 51,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,35</t>
+          <t>0,0; 27,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 54,66</t>
+          <t>7,53; 54,18</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,44</t>
+          <t>1,6; 14,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 22,48</t>
+          <t>7,22; 24,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 23,85</t>
+          <t>7,51; 22,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,06</t>
+          <t>5,35; 19,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,89; 26,75</t>
+          <t>9,82; 26,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 25,58</t>
+          <t>8,42; 25,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,03</t>
+          <t>5,02; 14,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 22,28</t>
+          <t>10,5; 21,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 21,17</t>
+          <t>9,61; 20,56</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4307</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4121</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3244</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2821</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2588</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3229</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>648; 4992</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>577; 5138</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3420</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2686</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2829</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>690; 5327</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3111</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3414</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1332; 6621</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2536</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2397</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3537</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4023</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3539</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>629; 4709</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>615; 4635</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>518; 4473</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3194</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9673</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3962</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>637; 5583</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1103; 5897</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>598; 4669</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3901; 12185</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1203; 6596</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5385; 14747</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1078; 6280</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>688; 5503</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>586; 4916</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2669</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>871; 7187</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>659; 6004</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2095</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2044</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2606</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>560; 3264</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3380</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>549; 3951</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>14692</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>663; 6184</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4379; 14609</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3964; 12118</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2498; 9219</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5756; 15760</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3871; 11664</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4431; 12740</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12524; 26028</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9490; 20301</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,88</t>
+          <t>0,0; 50,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,88</t>
+          <t>0,0; 44,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,49</t>
+          <t>0,0; 37,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,66</t>
+          <t>0,0; 43,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 32,73</t>
+          <t>4,22; 35,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 37,8</t>
+          <t>4,15; 36,16</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,18</t>
+          <t>0,0; 28,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,75</t>
+          <t>0,0; 62,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,69</t>
+          <t>0,0; 44,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 60,95</t>
+          <t>7,79; 56,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,26</t>
+          <t>0,0; 18,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 50,31</t>
+          <t>9,74; 47,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,14</t>
+          <t>0,0; 59,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,54</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,9</t>
+          <t>0,0; 52,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,49</t>
+          <t>0,0; 54,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,32</t>
+          <t>0,0; 51,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,35</t>
+          <t>0,0; 71,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 41,93</t>
+          <t>5,53; 42,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 30,12</t>
+          <t>4,08; 33,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 46,77</t>
+          <t>5,39; 44,76</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,65</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 32,16</t>
+          <t>3,72; 31,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 28,69</t>
+          <t>5,13; 27,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 30,51</t>
+          <t>3,91; 29,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 53,92</t>
+          <t>16,0; 52,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 22,64</t>
+          <t>4,28; 24,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 36,9</t>
+          <t>13,93; 38,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,78</t>
+          <t>2,81; 16,26</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 45,51</t>
+          <t>5,62; 46,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 47,86</t>
+          <t>5,8; 45,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,31</t>
+          <t>0,0; 28,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,92</t>
+          <t>0,0; 42,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 33,13</t>
+          <t>3,96; 31,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 33,91</t>
+          <t>3,84; 36,02</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,4</t>
+          <t>0,0; 68,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,41; 83,99</t>
+          <t>14,49; 83,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,38</t>
+          <t>0,0; 51,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,29</t>
+          <t>0,0; 32,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 54,18</t>
+          <t>7,54; 59,09</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,91</t>
+          <t>1,6; 14,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 24,07</t>
+          <t>7,08; 22,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,95</t>
+          <t>8,28; 23,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 19,74</t>
+          <t>5,49; 20,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 26,88</t>
+          <t>9,97; 27,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,42; 25,39</t>
+          <t>8,4; 25,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,45</t>
+          <t>4,45; 14,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,5; 21,81</t>
+          <t>10,08; 21,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 20,56</t>
+          <t>10,04; 21,5</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4307</t>
+          <t>0; 4346</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4121</t>
+          <t>0; 4314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 3279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2821</t>
+          <t>0; 2849</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 2974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>648; 4992</t>
+          <t>643; 5463</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>577; 5138</t>
+          <t>564; 4914</t>
         </is>
       </c>
     </row>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3420</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2686</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2829</t>
+          <t>0; 2713</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>690; 5327</t>
+          <t>681; 4928</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3111</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3414</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1332; 6621</t>
+          <t>1282; 6191</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2536</t>
+          <t>0; 2587</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 2914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2397</t>
+          <t>0; 2362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4023</t>
+          <t>0; 4031</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3539</t>
+          <t>0; 3619</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>629; 4709</t>
+          <t>621; 4790</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>615; 4635</t>
+          <t>628; 5226</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>518; 4473</t>
+          <t>515; 4280</t>
         </is>
       </c>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>637; 5583</t>
+          <t>645; 5528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1103; 5897</t>
+          <t>1055; 5721</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>598; 4669</t>
+          <t>599; 4572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3901; 12185</t>
+          <t>3616; 11866</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1203; 6596</t>
+          <t>1246; 7186</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5385; 14747</t>
+          <t>5567; 15197</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1078; 6280</t>
+          <t>1053; 6084</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>688; 5503</t>
+          <t>679; 5641</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>586; 4916</t>
+          <t>596; 4678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2714</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2669</t>
+          <t>0; 3169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>871; 7187</t>
+          <t>858; 6867</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>659; 6004</t>
+          <t>680; 6377</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2479,22 +2479,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>560; 3264</t>
+          <t>563; 3259</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 3379</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>549; 3951</t>
+          <t>550; 4309</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>663; 6184</t>
+          <t>662; 5810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4379; 14609</t>
+          <t>4296; 13609</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3964; 12118</t>
+          <t>4373; 12351</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2498; 9219</t>
+          <t>2566; 9752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5756; 15760</t>
+          <t>5849; 16263</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3871; 11664</t>
+          <t>3861; 11542</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4431; 12740</t>
+          <t>3927; 12593</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12524; 26028</t>
+          <t>12033; 25707</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9490; 20301</t>
+          <t>9909; 21228</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,69%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 37,32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 42,51</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 65,13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,33</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 44,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 37,88</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,07</t>
+          <t>0,0; 49,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,03</t>
+          <t>0,0; 46,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 22,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 35,83</t>
+          <t>4,25; 33,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 36,16</t>
+          <t>4,14; 38,95</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>15,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 44,5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,99</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,33</t>
+          <t>7,98; 60,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 56,38</t>
+          <t>0,0; 48,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>0,0; 25,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 19,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 47,04</t>
+          <t>9,73; 50,2</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,82%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,31</t>
+          <t>0,0; 51,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>0,0; 43,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,11</t>
+          <t>0,0; 72,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,14</t>
+          <t>0,0; 59,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,42</t>
+          <t>0,0; 36,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,94</t>
+          <t>0,0; 53,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 42,65</t>
+          <t>5,6; 42,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 33,96</t>
+          <t>4,05; 30,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 44,76</t>
+          <t>5,38; 50,07</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32,67%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,2%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,94%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>4,01; 30,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 31,84</t>
+          <t>16,52; 51,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 27,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 29,87</t>
+          <t>0,0; 30,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 52,51</t>
+          <t>3,78; 33,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,28; 28,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 24,67</t>
+          <t>4,29; 23,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 38,03</t>
+          <t>14,01; 38,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 16,26</t>
+          <t>2,96; 16,69</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,9%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,16%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 46,65</t>
+          <t>0,0; 28,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 45,54</t>
+          <t>0,0; 36,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,25</t>
+          <t>5,62; 46,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,64</t>
+          <t>5,58; 47,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 31,65</t>
+          <t>3,11; 29,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 36,02</t>
+          <t>3,66; 33,52</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>24,2%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>20,04%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,66</t>
+          <t>0,0; 68,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14,74; 83,74</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 70,35</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 68,3</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>14,49; 83,85</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,37</t>
+          <t>0,0; 52,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,83</t>
+          <t>0,0; 27,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 59,09</t>
+          <t>7,49; 54,66</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,2%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14,34%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,01</t>
+          <t>5,35; 20,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 22,43</t>
+          <t>9,89; 26,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 23,39</t>
+          <t>8,44; 25,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,88</t>
+          <t>1,5; 14,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,97; 27,73</t>
+          <t>6,87; 22,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,12</t>
+          <t>7,63; 23,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 14,28</t>
+          <t>4,49; 14,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 21,54</t>
+          <t>10,04; 22,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 21,5</t>
+          <t>9,65; 21,17</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1412</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3230</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2811</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2592</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4346</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4314</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3279</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2849</t>
+          <t>0; 4292</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2588</t>
+          <t>0; 4435</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>643; 5463</t>
+          <t>649; 5034</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>564; 4914</t>
+          <t>563; 5293</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>687</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2673</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 2697</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3519</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2756</t>
+          <t>697; 5282</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2713</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3569</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>681; 4928</t>
+          <t>0; 2153</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 3214</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3316</t>
+          <t>0; 3375</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1282; 6191</t>
+          <t>1281; 6607</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1372</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2587</t>
+          <t>0; 3523</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2914</t>
+          <t>0; 3436</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2362</t>
+          <t>0; 3657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3719</t>
+          <t>0; 2595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 2719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3619</t>
+          <t>0; 2407</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>621; 4790</t>
+          <t>629; 4739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>628; 5226</t>
+          <t>623; 4655</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>515; 4280</t>
+          <t>514; 4789</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2290</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2864</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7383</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>613; 4641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645; 5528</t>
+          <t>3734; 11701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1055; 5721</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>599; 4572</t>
+          <t>0; 4260</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3616; 11866</t>
+          <t>656; 5792</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1085; 5757</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1246; 7186</t>
+          <t>1251; 6909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5567; 15197</t>
+          <t>5597; 15344</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1053; 6084</t>
+          <t>1109; 6248</t>
         </is>
       </c>
     </row>
@@ -2190,27 +2190,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2407</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2071</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>679; 5641</t>
+          <t>0; 2774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>596; 4678</t>
+          <t>0; 2741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2714</t>
+          <t>680; 5575</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3169</t>
+          <t>573; 4929</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>858; 6867</t>
+          <t>675; 6340</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>680; 6377</t>
+          <t>648; 5934</t>
         </is>
       </c>
     </row>
@@ -2353,27 +2353,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>670</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1862</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2095</t>
+          <t>0; 2603</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>573; 3254</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2044</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2602</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>563; 3259</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>0; 3428</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3054</t>
+          <t>0; 2544</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>550; 4309</t>
+          <t>546; 3986</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>8010</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7570</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10024</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>662; 5810</t>
+          <t>2501; 9368</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4296; 13609</t>
+          <t>5800; 15687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4373; 12351</t>
+          <t>3878; 11752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2566; 9752</t>
+          <t>624; 5990</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5849; 16263</t>
+          <t>4172; 13644</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3861; 11542</t>
+          <t>4028; 12591</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3927; 12593</t>
+          <t>3963; 12374</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12033; 25707</t>
+          <t>11983; 26585</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9909; 21228</t>
+          <t>9528; 20905</t>
         </is>
       </c>
     </row>
